--- a/Excel/StockQuotation (5).xlsx
+++ b/Excel/StockQuotation (5).xlsx
@@ -402,7 +402,7 @@
         <v/>
       </c>
       <c r="C1" t="str">
-        <v>03/02/23 12:58:31</v>
+        <v>07/02/23 23:29:58</v>
       </c>
     </row>
     <row r="4">
@@ -426,34 +426,34 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>1038.25</v>
+        <v>1028.66</v>
       </c>
       <c r="B7" t="str">
-        <v>4.91 (0.4751%)</v>
+        <v>-4.29 (-0.4153%)</v>
       </c>
       <c r="C7" t="str">
         <v>High</v>
       </c>
       <c r="D7">
-        <v>1041.11</v>
+        <v>1035.46</v>
       </c>
       <c r="E7" t="str">
         <v>Low</v>
       </c>
       <c r="F7">
-        <v>1031.29</v>
+        <v>1022.95</v>
       </c>
       <c r="G7" t="str">
         <v>Volume</v>
       </c>
       <c r="H7">
-        <v>203547677</v>
+        <v>400196943</v>
       </c>
       <c r="I7" t="str">
         <v>Value</v>
       </c>
       <c r="J7">
-        <v>3698556718.79</v>
+        <v>8689032478.01</v>
       </c>
     </row>
     <row r="9">
@@ -514,22 +514,22 @@
         <v>-</v>
       </c>
       <c r="C10">
-        <v>21.6</v>
+        <v>21.1</v>
       </c>
       <c r="D10">
-        <v>0.2</v>
+        <v>-0.2</v>
       </c>
       <c r="E10">
-        <v>0.9345794392523364</v>
+        <v>-0.9389671361502347</v>
       </c>
       <c r="F10">
-        <v>21.5</v>
+        <v>21.3</v>
       </c>
       <c r="G10">
-        <v>21.7</v>
+        <v>21.4</v>
       </c>
       <c r="H10">
-        <v>21.4</v>
+        <v>20.9</v>
       </c>
       <c r="I10">
         <v>0</v>
@@ -538,22 +538,22 @@
         <v>0</v>
       </c>
       <c r="K10">
-        <v>6836436</v>
+        <v>11021734</v>
       </c>
       <c r="L10">
-        <v>147330.1925</v>
+        <v>232419.2244</v>
       </c>
       <c r="M10">
-        <v>853900</v>
+        <v>2048300</v>
       </c>
       <c r="N10">
-        <v>21.5</v>
+        <v>21</v>
       </c>
       <c r="O10">
-        <v>21.6</v>
+        <v>21.1</v>
       </c>
       <c r="P10">
-        <v>289200</v>
+        <v>189800</v>
       </c>
     </row>
     <row r="11">
@@ -564,46 +564,46 @@
         <v>-</v>
       </c>
       <c r="C11">
-        <v>29.75</v>
+        <v>29.5</v>
       </c>
       <c r="D11">
         <v>-0.25</v>
       </c>
       <c r="E11">
-        <v>-0.8333333333333334</v>
+        <v>-0.8403361344537815</v>
       </c>
       <c r="F11">
-        <v>29.75</v>
+        <v>30</v>
       </c>
       <c r="G11">
         <v>30</v>
       </c>
       <c r="H11">
+        <v>29.5</v>
+      </c>
+      <c r="I11">
+        <v>0</v>
+      </c>
+      <c r="J11">
+        <v>0</v>
+      </c>
+      <c r="K11">
+        <v>21781654</v>
+      </c>
+      <c r="L11">
+        <v>646621.64125</v>
+      </c>
+      <c r="M11">
+        <v>9700400</v>
+      </c>
+      <c r="N11">
+        <v>29.5</v>
+      </c>
+      <c r="O11">
         <v>29.75</v>
       </c>
-      <c r="I11">
-        <v>0</v>
-      </c>
-      <c r="J11">
-        <v>0</v>
-      </c>
-      <c r="K11">
-        <v>10127799</v>
-      </c>
-      <c r="L11">
-        <v>301787.20025</v>
-      </c>
-      <c r="M11">
-        <v>3463300</v>
-      </c>
-      <c r="N11">
-        <v>29.75</v>
-      </c>
-      <c r="O11">
-        <v>30</v>
-      </c>
       <c r="P11">
-        <v>3613300</v>
+        <v>1863000</v>
       </c>
     </row>
     <row r="12">
@@ -614,13 +614,13 @@
         <v>-</v>
       </c>
       <c r="C12">
-        <v>9.75</v>
+        <v>9.6</v>
       </c>
       <c r="D12">
-        <v>0</v>
+        <v>-0.15</v>
       </c>
       <c r="E12">
-        <v>0</v>
+        <v>-1.5384615384615385</v>
       </c>
       <c r="F12">
         <v>9.7</v>
@@ -629,31 +629,31 @@
         <v>9.75</v>
       </c>
       <c r="H12">
+        <v>9.55</v>
+      </c>
+      <c r="I12">
+        <v>0</v>
+      </c>
+      <c r="J12">
+        <v>0</v>
+      </c>
+      <c r="K12">
+        <v>58793587</v>
+      </c>
+      <c r="L12">
+        <v>565334.3098500001</v>
+      </c>
+      <c r="M12">
+        <v>1211000</v>
+      </c>
+      <c r="N12">
+        <v>9.6</v>
+      </c>
+      <c r="O12">
         <v>9.65</v>
       </c>
-      <c r="I12">
-        <v>0</v>
-      </c>
-      <c r="J12">
-        <v>0</v>
-      </c>
-      <c r="K12">
-        <v>8532159</v>
-      </c>
-      <c r="L12">
-        <v>82777.6208</v>
-      </c>
-      <c r="M12">
-        <v>4542200</v>
-      </c>
-      <c r="N12">
-        <v>9.7</v>
-      </c>
-      <c r="O12">
-        <v>9.75</v>
-      </c>
       <c r="P12">
-        <v>3210100</v>
+        <v>3215400</v>
       </c>
     </row>
     <row r="13">
@@ -664,46 +664,46 @@
         <v>-</v>
       </c>
       <c r="C13">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="D13">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="E13">
-        <v>0</v>
+        <v>-0.46511627906976744</v>
       </c>
       <c r="F13">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="G13">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="H13">
-        <v>216</v>
+        <v>211</v>
       </c>
       <c r="I13">
-        <v>0</v>
+        <v>13600</v>
       </c>
       <c r="J13">
-        <v>0</v>
+        <v>2910.4</v>
       </c>
       <c r="K13">
-        <v>789885</v>
+        <v>2593682</v>
       </c>
       <c r="L13">
-        <v>171059.342</v>
+        <v>553752.373</v>
       </c>
       <c r="M13">
-        <v>23000</v>
+        <v>315500</v>
       </c>
       <c r="N13">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="O13">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="P13">
-        <v>84200</v>
+        <v>204300</v>
       </c>
     </row>
     <row r="14">
@@ -714,46 +714,46 @@
         <v>-</v>
       </c>
       <c r="C14">
+        <v>38.5</v>
+      </c>
+      <c r="D14">
+        <v>0.5</v>
+      </c>
+      <c r="E14">
+        <v>1.3157894736842106</v>
+      </c>
+      <c r="F14">
         <v>38.25</v>
       </c>
-      <c r="D14">
-        <v>0.25</v>
-      </c>
-      <c r="E14">
-        <v>0.6578947368421053</v>
-      </c>
-      <c r="F14">
+      <c r="G14">
+        <v>38.75</v>
+      </c>
+      <c r="H14">
+        <v>37.5</v>
+      </c>
+      <c r="I14">
+        <v>0</v>
+      </c>
+      <c r="J14">
+        <v>0</v>
+      </c>
+      <c r="K14">
+        <v>4774943</v>
+      </c>
+      <c r="L14">
+        <v>182526.64975</v>
+      </c>
+      <c r="M14">
+        <v>374200</v>
+      </c>
+      <c r="N14">
         <v>38.5</v>
       </c>
-      <c r="G14">
-        <v>38.5</v>
-      </c>
-      <c r="H14">
-        <v>38</v>
-      </c>
-      <c r="I14">
-        <v>0</v>
-      </c>
-      <c r="J14">
-        <v>0</v>
-      </c>
-      <c r="K14">
-        <v>1713313</v>
-      </c>
-      <c r="L14">
-        <v>65550.448</v>
-      </c>
-      <c r="M14">
-        <v>146800</v>
-      </c>
-      <c r="N14">
-        <v>38.25</v>
-      </c>
       <c r="O14">
-        <v>38.5</v>
+        <v>38.75</v>
       </c>
       <c r="P14">
-        <v>651000</v>
+        <v>403100</v>
       </c>
     </row>
     <row r="15">
@@ -764,22 +764,22 @@
         <v>-</v>
       </c>
       <c r="C15">
-        <v>8.4</v>
+        <v>8.25</v>
       </c>
       <c r="D15">
         <v>-0.05</v>
       </c>
       <c r="E15">
-        <v>-0.591715976331361</v>
+        <v>-0.6024096385542169</v>
       </c>
       <c r="F15">
+        <v>8.3</v>
+      </c>
+      <c r="G15">
         <v>8.4</v>
       </c>
-      <c r="G15">
-        <v>8.45</v>
-      </c>
       <c r="H15">
-        <v>8.4</v>
+        <v>8.2</v>
       </c>
       <c r="I15">
         <v>0</v>
@@ -788,22 +788,22 @@
         <v>0</v>
       </c>
       <c r="K15">
-        <v>6616794</v>
+        <v>52782066</v>
       </c>
       <c r="L15">
-        <v>55847.0761</v>
+        <v>436595.46095</v>
       </c>
       <c r="M15">
-        <v>5078500</v>
+        <v>267700</v>
       </c>
       <c r="N15">
-        <v>8.4</v>
+        <v>8.25</v>
       </c>
       <c r="O15">
-        <v>8.45</v>
+        <v>8.3</v>
       </c>
       <c r="P15">
-        <v>1630800</v>
+        <v>1769900</v>
       </c>
     </row>
     <row r="16">
@@ -814,22 +814,22 @@
         <v>-</v>
       </c>
       <c r="C16">
-        <v>103.5</v>
+        <v>102</v>
       </c>
       <c r="D16">
-        <v>0.5</v>
+        <v>-1</v>
       </c>
       <c r="E16">
-        <v>0.4854368932038835</v>
+        <v>-0.970873786407767</v>
       </c>
       <c r="F16">
-        <v>103.5</v>
+        <v>103</v>
       </c>
       <c r="G16">
         <v>103.5</v>
       </c>
       <c r="H16">
-        <v>102.5</v>
+        <v>101.5</v>
       </c>
       <c r="I16">
         <v>0</v>
@@ -838,22 +838,22 @@
         <v>0</v>
       </c>
       <c r="K16">
-        <v>596127</v>
+        <v>1768116</v>
       </c>
       <c r="L16">
-        <v>61450.2335</v>
+        <v>180572.946</v>
       </c>
       <c r="M16">
-        <v>137100</v>
+        <v>151600</v>
       </c>
       <c r="N16">
-        <v>103</v>
+        <v>101.5</v>
       </c>
       <c r="O16">
-        <v>103.5</v>
+        <v>102</v>
       </c>
       <c r="P16">
-        <v>282300</v>
+        <v>63900</v>
       </c>
     </row>
     <row r="17">
@@ -864,46 +864,46 @@
         <v>-</v>
       </c>
       <c r="C17">
-        <v>3.9</v>
+        <v>3.88</v>
       </c>
       <c r="D17">
-        <v>-0.12</v>
+        <v>-0.04</v>
       </c>
       <c r="E17">
-        <v>-2.985074626865672</v>
+        <v>-1.0204081632653061</v>
       </c>
       <c r="F17">
-        <v>4.02</v>
+        <v>3.92</v>
       </c>
       <c r="G17">
-        <v>4.02</v>
+        <v>3.92</v>
       </c>
       <c r="H17">
+        <v>3.84</v>
+      </c>
+      <c r="I17">
+        <v>0</v>
+      </c>
+      <c r="J17">
+        <v>0</v>
+      </c>
+      <c r="K17">
+        <v>34601807</v>
+      </c>
+      <c r="L17">
+        <v>133738.43502</v>
+      </c>
+      <c r="M17">
+        <v>1579900</v>
+      </c>
+      <c r="N17">
         <v>3.86</v>
       </c>
-      <c r="I17">
-        <v>0</v>
-      </c>
-      <c r="J17">
-        <v>0</v>
-      </c>
-      <c r="K17">
-        <v>65572992</v>
-      </c>
-      <c r="L17">
-        <v>257050.73036000002</v>
-      </c>
-      <c r="M17">
-        <v>1628200</v>
-      </c>
-      <c r="N17">
+      <c r="O17">
         <v>3.88</v>
       </c>
-      <c r="O17">
-        <v>3.9</v>
-      </c>
       <c r="P17">
-        <v>2800600</v>
+        <v>1263300</v>
       </c>
     </row>
     <row r="18">
@@ -914,46 +914,46 @@
         <v>-</v>
       </c>
       <c r="C18">
-        <v>32.5</v>
+        <v>31.75</v>
       </c>
       <c r="D18">
-        <v>0</v>
+        <v>-0.5</v>
       </c>
       <c r="E18">
-        <v>0</v>
+        <v>-1.550387596899225</v>
       </c>
       <c r="F18">
-        <v>32.5</v>
+        <v>32</v>
       </c>
       <c r="G18">
-        <v>32.75</v>
+        <v>32.25</v>
       </c>
       <c r="H18">
+        <v>31.25</v>
+      </c>
+      <c r="I18">
+        <v>7133000</v>
+      </c>
+      <c r="J18">
+        <v>228106</v>
+      </c>
+      <c r="K18">
+        <v>15549744</v>
+      </c>
+      <c r="L18">
+        <v>495102.87975</v>
+      </c>
+      <c r="M18">
+        <v>265700</v>
+      </c>
+      <c r="N18">
+        <v>31.75</v>
+      </c>
+      <c r="O18">
         <v>32</v>
       </c>
-      <c r="I18">
-        <v>0</v>
-      </c>
-      <c r="J18">
-        <v>0</v>
-      </c>
-      <c r="K18">
-        <v>7897929</v>
-      </c>
-      <c r="L18">
-        <v>253918.7285</v>
-      </c>
-      <c r="M18">
-        <v>167600</v>
-      </c>
-      <c r="N18">
-        <v>32.25</v>
-      </c>
-      <c r="O18">
-        <v>32.5</v>
-      </c>
       <c r="P18">
-        <v>1216400</v>
+        <v>667600</v>
       </c>
     </row>
     <row r="19">
@@ -964,19 +964,19 @@
         <v>-</v>
       </c>
       <c r="C19">
-        <v>67.5</v>
+        <v>66.75</v>
       </c>
       <c r="D19">
-        <v>0.75</v>
+        <v>0</v>
       </c>
       <c r="E19">
-        <v>1.1235955056179776</v>
+        <v>0</v>
       </c>
       <c r="F19">
-        <v>66.75</v>
+        <v>66.5</v>
       </c>
       <c r="G19">
-        <v>67.5</v>
+        <v>67</v>
       </c>
       <c r="H19">
         <v>66.5</v>
@@ -988,22 +988,22 @@
         <v>0</v>
       </c>
       <c r="K19">
-        <v>5993135</v>
+        <v>17353807</v>
       </c>
       <c r="L19">
-        <v>401516.93475</v>
+        <v>1158120.88375</v>
       </c>
       <c r="M19">
-        <v>848500</v>
+        <v>2792200</v>
       </c>
       <c r="N19">
-        <v>67.25</v>
+        <v>66.75</v>
       </c>
       <c r="O19">
-        <v>67.5</v>
+        <v>67</v>
       </c>
       <c r="P19">
-        <v>928200</v>
+        <v>1848100</v>
       </c>
     </row>
     <row r="20">
@@ -1014,7 +1014,7 @@
         <v>-</v>
       </c>
       <c r="C20">
-        <v>23.8</v>
+        <v>23.6</v>
       </c>
       <c r="D20">
         <v>0</v>
@@ -1023,13 +1023,13 @@
         <v>0</v>
       </c>
       <c r="F20">
-        <v>23.8</v>
+        <v>23.6</v>
       </c>
       <c r="G20">
-        <v>24</v>
+        <v>23.7</v>
       </c>
       <c r="H20">
-        <v>23.7</v>
+        <v>23.5</v>
       </c>
       <c r="I20">
         <v>0</v>
@@ -1038,22 +1038,22 @@
         <v>0</v>
       </c>
       <c r="K20">
-        <v>9578760</v>
+        <v>17028962</v>
       </c>
       <c r="L20">
-        <v>228593.6587</v>
+        <v>401183.07739999995</v>
       </c>
       <c r="M20">
-        <v>1523800</v>
+        <v>2056100</v>
       </c>
       <c r="N20">
-        <v>23.8</v>
+        <v>23.5</v>
       </c>
       <c r="O20">
-        <v>23.9</v>
+        <v>23.6</v>
       </c>
       <c r="P20">
-        <v>474400</v>
+        <v>347500</v>
       </c>
     </row>
     <row r="21">
@@ -1064,19 +1064,19 @@
         <v>-</v>
       </c>
       <c r="C21">
+        <v>44.25</v>
+      </c>
+      <c r="D21">
+        <v>-0.25</v>
+      </c>
+      <c r="E21">
+        <v>-0.5617977528089888</v>
+      </c>
+      <c r="F21">
         <v>44.5</v>
       </c>
-      <c r="D21">
-        <v>0.25</v>
-      </c>
-      <c r="E21">
-        <v>0.5649717514124294</v>
-      </c>
-      <c r="F21">
-        <v>44</v>
-      </c>
       <c r="G21">
-        <v>44.75</v>
+        <v>44.5</v>
       </c>
       <c r="H21">
         <v>43.75</v>
@@ -1088,22 +1088,22 @@
         <v>0</v>
       </c>
       <c r="K21">
-        <v>5789252</v>
+        <v>10167453</v>
       </c>
       <c r="L21">
-        <v>255629.49225</v>
+        <v>448185.82275</v>
       </c>
       <c r="M21">
-        <v>1007200</v>
+        <v>667100</v>
       </c>
       <c r="N21">
-        <v>44.5</v>
+        <v>44</v>
       </c>
       <c r="O21">
-        <v>44.75</v>
+        <v>44.25</v>
       </c>
       <c r="P21">
-        <v>888400</v>
+        <v>1198400</v>
       </c>
     </row>
     <row r="22">
@@ -1114,19 +1114,19 @@
         <v>-</v>
       </c>
       <c r="C22">
-        <v>14.2</v>
+        <v>13.9</v>
       </c>
       <c r="D22">
-        <v>0.5</v>
+        <v>-0.1</v>
       </c>
       <c r="E22">
-        <v>3.6496350364963503</v>
+        <v>-0.7142857142857143</v>
       </c>
       <c r="F22">
-        <v>13.8</v>
+        <v>14</v>
       </c>
       <c r="G22">
-        <v>14.4</v>
+        <v>14.1</v>
       </c>
       <c r="H22">
         <v>13.8</v>
@@ -1138,22 +1138,22 @@
         <v>0</v>
       </c>
       <c r="K22">
-        <v>13229652</v>
+        <v>8237603</v>
       </c>
       <c r="L22">
-        <v>187884.317</v>
+        <v>114980.3154</v>
       </c>
       <c r="M22">
-        <v>880300</v>
+        <v>348700</v>
       </c>
       <c r="N22">
-        <v>14.2</v>
+        <v>13.9</v>
       </c>
       <c r="O22">
-        <v>14.3</v>
+        <v>14</v>
       </c>
       <c r="P22">
-        <v>590500</v>
+        <v>1020100</v>
       </c>
     </row>
     <row r="23">
@@ -1164,19 +1164,19 @@
         <v>-</v>
       </c>
       <c r="C23">
-        <v>21.1</v>
+        <v>20.9</v>
       </c>
       <c r="D23">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="E23">
-        <v>1.932367149758454</v>
+        <v>0</v>
       </c>
       <c r="F23">
-        <v>20.8</v>
+        <v>20.9</v>
       </c>
       <c r="G23">
-        <v>21.2</v>
+        <v>21</v>
       </c>
       <c r="H23">
         <v>20.7</v>
@@ -1188,22 +1188,22 @@
         <v>0</v>
       </c>
       <c r="K23">
-        <v>7827538</v>
+        <v>11074770</v>
       </c>
       <c r="L23">
-        <v>164164.5855</v>
+        <v>230826.29940000002</v>
       </c>
       <c r="M23">
-        <v>366800</v>
+        <v>9800</v>
       </c>
       <c r="N23">
-        <v>21.1</v>
+        <v>20.9</v>
       </c>
       <c r="O23">
-        <v>21.2</v>
+        <v>21</v>
       </c>
       <c r="P23">
-        <v>1111100</v>
+        <v>851900</v>
       </c>
     </row>
     <row r="24">
@@ -1214,22 +1214,22 @@
         <v>-</v>
       </c>
       <c r="C24">
-        <v>14.9</v>
+        <v>14.7</v>
       </c>
       <c r="D24">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="E24">
-        <v>3.4722222222222223</v>
+        <v>0</v>
       </c>
       <c r="F24">
-        <v>14.5</v>
+        <v>14.7</v>
       </c>
       <c r="G24">
-        <v>14.9</v>
+        <v>14.8</v>
       </c>
       <c r="H24">
-        <v>14.4</v>
+        <v>14.6</v>
       </c>
       <c r="I24">
         <v>0</v>
@@ -1238,22 +1238,22 @@
         <v>0</v>
       </c>
       <c r="K24">
-        <v>17087624</v>
+        <v>11804881</v>
       </c>
       <c r="L24">
-        <v>251533.164</v>
+        <v>173815.2965</v>
       </c>
       <c r="M24">
-        <v>2459500</v>
+        <v>2315500</v>
       </c>
       <c r="N24">
+        <v>14.7</v>
+      </c>
+      <c r="O24">
         <v>14.8</v>
       </c>
-      <c r="O24">
-        <v>14.9</v>
-      </c>
       <c r="P24">
-        <v>2476200</v>
+        <v>1376800</v>
       </c>
     </row>
     <row r="25">
@@ -1264,22 +1264,22 @@
         <v>-</v>
       </c>
       <c r="C25">
-        <v>21.3</v>
+        <v>20.7</v>
       </c>
       <c r="D25">
-        <v>0.1</v>
+        <v>-0.2</v>
       </c>
       <c r="E25">
-        <v>0.4716981132075472</v>
+        <v>-0.9569377990430622</v>
       </c>
       <c r="F25">
-        <v>21.2</v>
+        <v>20.8</v>
       </c>
       <c r="G25">
-        <v>21.4</v>
+        <v>21</v>
       </c>
       <c r="H25">
-        <v>21.2</v>
+        <v>20.5</v>
       </c>
       <c r="I25">
         <v>0</v>
@@ -1288,22 +1288,22 @@
         <v>0</v>
       </c>
       <c r="K25">
-        <v>1299710</v>
+        <v>5033514</v>
       </c>
       <c r="L25">
-        <v>27678.966</v>
+        <v>104421.0835</v>
       </c>
       <c r="M25">
-        <v>134500</v>
+        <v>167300</v>
       </c>
       <c r="N25">
-        <v>21.3</v>
+        <v>20.6</v>
       </c>
       <c r="O25">
-        <v>21.4</v>
+        <v>20.7</v>
       </c>
       <c r="P25">
-        <v>109800</v>
+        <v>10300</v>
       </c>
     </row>
     <row r="26">
@@ -1314,22 +1314,22 @@
         <v>-</v>
       </c>
       <c r="C26">
+        <v>18.3</v>
+      </c>
+      <c r="D26">
+        <v>-0.3</v>
+      </c>
+      <c r="E26">
+        <v>-1.6129032258064515</v>
+      </c>
+      <c r="F26">
+        <v>18.6</v>
+      </c>
+      <c r="G26">
         <v>18.7</v>
       </c>
-      <c r="D26">
-        <v>0.1</v>
-      </c>
-      <c r="E26">
-        <v>0.5376344086021505</v>
-      </c>
-      <c r="F26">
-        <v>18.9</v>
-      </c>
-      <c r="G26">
-        <v>19</v>
-      </c>
       <c r="H26">
-        <v>18.5</v>
+        <v>18.2</v>
       </c>
       <c r="I26">
         <v>0</v>
@@ -1338,22 +1338,22 @@
         <v>0</v>
       </c>
       <c r="K26">
-        <v>976661</v>
+        <v>2231293</v>
       </c>
       <c r="L26">
-        <v>18309.578</v>
+        <v>40973.5248</v>
       </c>
       <c r="M26">
-        <v>144400</v>
+        <v>130400</v>
       </c>
       <c r="N26">
-        <v>18.6</v>
+        <v>18.3</v>
       </c>
       <c r="O26">
-        <v>18.7</v>
+        <v>18.4</v>
       </c>
       <c r="P26">
-        <v>84300</v>
+        <v>30900</v>
       </c>
     </row>
     <row r="27">
@@ -1364,46 +1364,46 @@
         <v>-</v>
       </c>
       <c r="C27">
-        <v>57.25</v>
+        <v>56.25</v>
       </c>
       <c r="D27">
-        <v>0.5</v>
+        <v>-0.5</v>
       </c>
       <c r="E27">
-        <v>0.8810572687224669</v>
+        <v>-0.8810572687224669</v>
       </c>
       <c r="F27">
         <v>56.75</v>
       </c>
       <c r="G27">
-        <v>57.5</v>
+        <v>57</v>
       </c>
       <c r="H27">
+        <v>56</v>
+      </c>
+      <c r="I27">
+        <v>0</v>
+      </c>
+      <c r="J27">
+        <v>0</v>
+      </c>
+      <c r="K27">
+        <v>1610798</v>
+      </c>
+      <c r="L27">
+        <v>90754.65875</v>
+      </c>
+      <c r="M27">
+        <v>165800</v>
+      </c>
+      <c r="N27">
+        <v>56.25</v>
+      </c>
+      <c r="O27">
         <v>56.5</v>
       </c>
-      <c r="I27">
-        <v>0</v>
-      </c>
-      <c r="J27">
-        <v>0</v>
-      </c>
-      <c r="K27">
-        <v>357847</v>
-      </c>
-      <c r="L27">
-        <v>20421.24775</v>
-      </c>
-      <c r="M27">
-        <v>161800</v>
-      </c>
-      <c r="N27">
-        <v>57</v>
-      </c>
-      <c r="O27">
-        <v>57.25</v>
-      </c>
       <c r="P27">
-        <v>39500</v>
+        <v>77200</v>
       </c>
     </row>
     <row r="28">
@@ -1417,19 +1417,19 @@
         <v>51.5</v>
       </c>
       <c r="D28">
-        <v>-0.5</v>
+        <v>-0.25</v>
       </c>
       <c r="E28">
-        <v>-0.9615384615384616</v>
+        <v>-0.4830917874396135</v>
       </c>
       <c r="F28">
-        <v>52</v>
+        <v>51.75</v>
       </c>
       <c r="G28">
         <v>52</v>
       </c>
       <c r="H28">
-        <v>51.25</v>
+        <v>50.5</v>
       </c>
       <c r="I28">
         <v>0</v>
@@ -1438,22 +1438,22 @@
         <v>0</v>
       </c>
       <c r="K28">
-        <v>837619</v>
+        <v>2419856</v>
       </c>
       <c r="L28">
-        <v>43140.9105</v>
+        <v>124190.05275</v>
       </c>
       <c r="M28">
-        <v>221800</v>
+        <v>307500</v>
       </c>
       <c r="N28">
-        <v>51.25</v>
+        <v>51.5</v>
       </c>
       <c r="O28">
-        <v>51.5</v>
+        <v>51.75</v>
       </c>
       <c r="P28">
-        <v>67600</v>
+        <v>22200</v>
       </c>
     </row>
     <row r="29">
@@ -1464,13 +1464,13 @@
         <v>-</v>
       </c>
       <c r="C29">
-        <v>28.25</v>
+        <v>28.5</v>
       </c>
       <c r="D29">
-        <v>-0.25</v>
+        <v>0.25</v>
       </c>
       <c r="E29">
-        <v>-0.8771929824561403</v>
+        <v>0.8849557522123894</v>
       </c>
       <c r="F29">
         <v>28.25</v>
@@ -1479,7 +1479,7 @@
         <v>28.5</v>
       </c>
       <c r="H29">
-        <v>28.25</v>
+        <v>28</v>
       </c>
       <c r="I29">
         <v>0</v>
@@ -1488,13 +1488,13 @@
         <v>0</v>
       </c>
       <c r="K29">
-        <v>1108746</v>
+        <v>5471542</v>
       </c>
       <c r="L29">
-        <v>31330.526</v>
+        <v>154774.204</v>
       </c>
       <c r="M29">
-        <v>639800</v>
+        <v>760700</v>
       </c>
       <c r="N29">
         <v>28.25</v>
@@ -1503,7 +1503,7 @@
         <v>28.5</v>
       </c>
       <c r="P29">
-        <v>1398300</v>
+        <v>714100</v>
       </c>
     </row>
     <row r="30">
@@ -1514,19 +1514,19 @@
         <v>-</v>
       </c>
       <c r="C30">
-        <v>54.5</v>
+        <v>54.25</v>
       </c>
       <c r="D30">
-        <v>0.25</v>
+        <v>-0.25</v>
       </c>
       <c r="E30">
-        <v>0.4608294930875576</v>
+        <v>-0.45871559633027525</v>
       </c>
       <c r="F30">
-        <v>54.25</v>
+        <v>54.75</v>
       </c>
       <c r="G30">
-        <v>54.5</v>
+        <v>54.75</v>
       </c>
       <c r="H30">
         <v>54</v>
@@ -1538,22 +1538,22 @@
         <v>0</v>
       </c>
       <c r="K30">
-        <v>32207</v>
+        <v>119773</v>
       </c>
       <c r="L30">
-        <v>1748.2065</v>
+        <v>6501.21925</v>
       </c>
       <c r="M30">
-        <v>131400</v>
+        <v>112400</v>
       </c>
       <c r="N30">
         <v>54</v>
       </c>
       <c r="O30">
-        <v>54.5</v>
+        <v>54.25</v>
       </c>
       <c r="P30">
-        <v>20200</v>
+        <v>4600</v>
       </c>
     </row>
     <row r="31">
@@ -1564,46 +1564,46 @@
         <v>-</v>
       </c>
       <c r="C31">
-        <v>13</v>
+        <v>12.9</v>
       </c>
       <c r="D31">
         <v>0.1</v>
       </c>
       <c r="E31">
-        <v>0.7751937984496124</v>
+        <v>0.78125</v>
       </c>
       <c r="F31">
+        <v>12.8</v>
+      </c>
+      <c r="G31">
         <v>13</v>
       </c>
-      <c r="G31">
-        <v>13.1</v>
-      </c>
       <c r="H31">
+        <v>12.8</v>
+      </c>
+      <c r="I31">
+        <v>0</v>
+      </c>
+      <c r="J31">
+        <v>0</v>
+      </c>
+      <c r="K31">
+        <v>3377331</v>
+      </c>
+      <c r="L31">
+        <v>43600.9581</v>
+      </c>
+      <c r="M31">
+        <v>334900</v>
+      </c>
+      <c r="N31">
+        <v>12.8</v>
+      </c>
+      <c r="O31">
         <v>12.9</v>
       </c>
-      <c r="I31">
-        <v>0</v>
-      </c>
-      <c r="J31">
-        <v>0</v>
-      </c>
-      <c r="K31">
-        <v>688022</v>
-      </c>
-      <c r="L31">
-        <v>8931.6222</v>
-      </c>
-      <c r="M31">
-        <v>214500</v>
-      </c>
-      <c r="N31">
-        <v>12.9</v>
-      </c>
-      <c r="O31">
-        <v>13</v>
-      </c>
       <c r="P31">
-        <v>327700</v>
+        <v>419300</v>
       </c>
     </row>
     <row r="32">
@@ -1617,19 +1617,19 @@
         <v>31</v>
       </c>
       <c r="D32">
-        <v>0.75</v>
+        <v>0</v>
       </c>
       <c r="E32">
-        <v>2.479338842975207</v>
+        <v>0</v>
       </c>
       <c r="F32">
-        <v>30.5</v>
+        <v>31</v>
       </c>
       <c r="G32">
-        <v>31</v>
+        <v>31.25</v>
       </c>
       <c r="H32">
-        <v>30.5</v>
+        <v>30.75</v>
       </c>
       <c r="I32">
         <v>0</v>
@@ -1638,13 +1638,13 @@
         <v>0</v>
       </c>
       <c r="K32">
-        <v>1326990</v>
+        <v>1864108</v>
       </c>
       <c r="L32">
-        <v>40796.9215</v>
+        <v>57752.77575</v>
       </c>
       <c r="M32">
-        <v>209300</v>
+        <v>385200</v>
       </c>
       <c r="N32">
         <v>30.75</v>
@@ -1653,7 +1653,7 @@
         <v>31</v>
       </c>
       <c r="P32">
-        <v>536800</v>
+        <v>96800</v>
       </c>
     </row>
     <row r="33">
@@ -1664,22 +1664,22 @@
         <v>-</v>
       </c>
       <c r="C33">
-        <v>13.1</v>
+        <v>13</v>
       </c>
       <c r="D33">
-        <v>0.3</v>
+        <v>-0.4</v>
       </c>
       <c r="E33">
-        <v>2.34375</v>
+        <v>-2.985074626865672</v>
       </c>
       <c r="F33">
-        <v>12.8</v>
+        <v>13.5</v>
       </c>
       <c r="G33">
-        <v>13.2</v>
+        <v>13.5</v>
       </c>
       <c r="H33">
-        <v>12.8</v>
+        <v>13</v>
       </c>
       <c r="I33">
         <v>0</v>
@@ -1688,13 +1688,13 @@
         <v>0</v>
       </c>
       <c r="K33">
-        <v>14558596</v>
+        <v>41170399</v>
       </c>
       <c r="L33">
-        <v>188921.5887</v>
+        <v>542325.5884</v>
       </c>
       <c r="M33">
-        <v>1242300</v>
+        <v>104800</v>
       </c>
       <c r="N33">
         <v>13</v>
@@ -1703,7 +1703,7 @@
         <v>13.1</v>
       </c>
       <c r="P33">
-        <v>2153000</v>
+        <v>359200</v>
       </c>
     </row>
     <row r="34">
@@ -1714,46 +1714,46 @@
         <v>-</v>
       </c>
       <c r="C34">
-        <v>28.5</v>
+        <v>28</v>
       </c>
       <c r="D34">
-        <v>0</v>
+        <v>-0.25</v>
       </c>
       <c r="E34">
-        <v>0</v>
+        <v>-0.8849557522123894</v>
       </c>
       <c r="F34">
         <v>28.5</v>
       </c>
       <c r="G34">
-        <v>28.75</v>
+        <v>28.5</v>
       </c>
       <c r="H34">
+        <v>28</v>
+      </c>
+      <c r="I34">
+        <v>0</v>
+      </c>
+      <c r="J34">
+        <v>0</v>
+      </c>
+      <c r="K34">
+        <v>1866964</v>
+      </c>
+      <c r="L34">
+        <v>52523.9265</v>
+      </c>
+      <c r="M34">
+        <v>56300</v>
+      </c>
+      <c r="N34">
+        <v>28</v>
+      </c>
+      <c r="O34">
         <v>28.25</v>
       </c>
-      <c r="I34">
-        <v>0</v>
-      </c>
-      <c r="J34">
-        <v>0</v>
-      </c>
-      <c r="K34">
-        <v>1709408</v>
-      </c>
-      <c r="L34">
-        <v>48599.07775</v>
-      </c>
-      <c r="M34">
-        <v>449900</v>
-      </c>
-      <c r="N34">
-        <v>28.25</v>
-      </c>
-      <c r="O34">
-        <v>28.5</v>
-      </c>
       <c r="P34">
-        <v>193200</v>
+        <v>79900</v>
       </c>
     </row>
     <row r="35">
@@ -1764,22 +1764,22 @@
         <v>-</v>
       </c>
       <c r="C35">
-        <v>22.5</v>
+        <v>23.4</v>
       </c>
       <c r="D35">
-        <v>-0.2</v>
+        <v>0.8</v>
       </c>
       <c r="E35">
-        <v>-0.8810572687224669</v>
+        <v>3.5398230088495577</v>
       </c>
       <c r="F35">
-        <v>22.4</v>
+        <v>22.6</v>
       </c>
       <c r="G35">
-        <v>22.7</v>
+        <v>23.6</v>
       </c>
       <c r="H35">
-        <v>22.2</v>
+        <v>22.6</v>
       </c>
       <c r="I35">
         <v>0</v>
@@ -1788,22 +1788,22 @@
         <v>0</v>
       </c>
       <c r="K35">
-        <v>3373962</v>
+        <v>17792391</v>
       </c>
       <c r="L35">
-        <v>75963.40740000001</v>
+        <v>410653.2648</v>
       </c>
       <c r="M35">
-        <v>371100</v>
+        <v>371800</v>
       </c>
       <c r="N35">
-        <v>22.5</v>
+        <v>23.3</v>
       </c>
       <c r="O35">
-        <v>22.6</v>
+        <v>23.4</v>
       </c>
       <c r="P35">
-        <v>127500</v>
+        <v>22700</v>
       </c>
     </row>
     <row r="36">
@@ -1814,22 +1814,22 @@
         <v>-</v>
       </c>
       <c r="C36">
-        <v>70.5</v>
+        <v>68</v>
       </c>
       <c r="D36">
-        <v>0.5</v>
+        <v>-3.25</v>
       </c>
       <c r="E36">
-        <v>0.7142857142857143</v>
+        <v>-4.56140350877193</v>
       </c>
       <c r="F36">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G36">
-        <v>71</v>
+        <v>71.75</v>
       </c>
       <c r="H36">
-        <v>69.75</v>
+        <v>67</v>
       </c>
       <c r="I36">
         <v>0</v>
@@ -1838,22 +1838,22 @@
         <v>0</v>
       </c>
       <c r="K36">
-        <v>3169710</v>
+        <v>11758723</v>
       </c>
       <c r="L36">
-        <v>223362.629</v>
+        <v>805737.68375</v>
       </c>
       <c r="M36">
-        <v>111300</v>
+        <v>68100</v>
       </c>
       <c r="N36">
-        <v>70.25</v>
+        <v>68</v>
       </c>
       <c r="O36">
-        <v>70.5</v>
+        <v>68.25</v>
       </c>
       <c r="P36">
-        <v>131200</v>
+        <v>55900</v>
       </c>
     </row>
     <row r="37">
@@ -1867,43 +1867,43 @@
         <v>16.2</v>
       </c>
       <c r="D37">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="E37">
-        <v>0.6211180124223602</v>
+        <v>0</v>
       </c>
       <c r="F37">
+        <v>16.3</v>
+      </c>
+      <c r="G37">
+        <v>16.4</v>
+      </c>
+      <c r="H37">
         <v>16.1</v>
       </c>
-      <c r="G37">
+      <c r="I37">
+        <v>0</v>
+      </c>
+      <c r="J37">
+        <v>0</v>
+      </c>
+      <c r="K37">
+        <v>16289493</v>
+      </c>
+      <c r="L37">
+        <v>264277.7181</v>
+      </c>
+      <c r="M37">
+        <v>1328900</v>
+      </c>
+      <c r="N37">
         <v>16.2</v>
       </c>
-      <c r="H37">
-        <v>16</v>
-      </c>
-      <c r="I37">
-        <v>0</v>
-      </c>
-      <c r="J37">
-        <v>0</v>
-      </c>
-      <c r="K37">
-        <v>4613789</v>
-      </c>
-      <c r="L37">
-        <v>74294.3007</v>
-      </c>
-      <c r="M37">
-        <v>1120400</v>
-      </c>
-      <c r="N37">
-        <v>16.1</v>
-      </c>
       <c r="O37">
-        <v>16.2</v>
+        <v>16.3</v>
       </c>
       <c r="P37">
-        <v>2225000</v>
+        <v>1582700</v>
       </c>
     </row>
     <row r="38">
@@ -1914,46 +1914,46 @@
         <v>-</v>
       </c>
       <c r="C38">
-        <v>29.25</v>
+        <v>28.75</v>
       </c>
       <c r="D38">
-        <v>0</v>
+        <v>-0.25</v>
       </c>
       <c r="E38">
-        <v>0</v>
+        <v>-0.8620689655172413</v>
       </c>
       <c r="F38">
-        <v>29.25</v>
+        <v>29</v>
       </c>
       <c r="G38">
         <v>29.25</v>
       </c>
       <c r="H38">
+        <v>28.75</v>
+      </c>
+      <c r="I38">
+        <v>0</v>
+      </c>
+      <c r="J38">
+        <v>0</v>
+      </c>
+      <c r="K38">
+        <v>298190</v>
+      </c>
+      <c r="L38">
+        <v>8600.59175</v>
+      </c>
+      <c r="M38">
+        <v>1106000</v>
+      </c>
+      <c r="N38">
+        <v>28.75</v>
+      </c>
+      <c r="O38">
         <v>29</v>
       </c>
-      <c r="I38">
-        <v>0</v>
-      </c>
-      <c r="J38">
-        <v>0</v>
-      </c>
-      <c r="K38">
-        <v>205476</v>
-      </c>
-      <c r="L38">
-        <v>5990.7045</v>
-      </c>
-      <c r="M38">
-        <v>476300</v>
-      </c>
-      <c r="N38">
-        <v>29</v>
-      </c>
-      <c r="O38">
-        <v>29.25</v>
-      </c>
       <c r="P38">
-        <v>739100</v>
+        <v>64100</v>
       </c>
     </row>
     <row r="39">
@@ -1964,23 +1964,23 @@
         <v>-</v>
       </c>
       <c r="C39">
+        <v>2.78</v>
+      </c>
+      <c r="D39">
+        <v>0.04</v>
+      </c>
+      <c r="E39">
+        <v>1.4598540145985401</v>
+      </c>
+      <c r="F39">
+        <v>2.74</v>
+      </c>
+      <c r="G39">
+        <v>2.8</v>
+      </c>
+      <c r="H39">
         <v>2.72</v>
       </c>
-      <c r="D39">
-        <v>-0.02</v>
-      </c>
-      <c r="E39">
-        <v>-0.7299270072992701</v>
-      </c>
-      <c r="F39">
-        <v>2.7</v>
-      </c>
-      <c r="G39">
-        <v>2.72</v>
-      </c>
-      <c r="H39">
-        <v>2.7</v>
-      </c>
       <c r="I39">
         <v>0</v>
       </c>
@@ -1988,22 +1988,22 @@
         <v>0</v>
       </c>
       <c r="K39">
-        <v>1099539</v>
+        <v>9523459</v>
       </c>
       <c r="L39">
-        <v>2973.3080800000002</v>
+        <v>26306.11264</v>
       </c>
       <c r="M39">
-        <v>1659200</v>
+        <v>214400</v>
       </c>
       <c r="N39">
-        <v>2.7</v>
+        <v>2.76</v>
       </c>
       <c r="O39">
-        <v>2.72</v>
+        <v>2.78</v>
       </c>
       <c r="P39">
-        <v>560800</v>
+        <v>650900</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/StockQuotation (5).xlsx
+++ b/Excel/StockQuotation (5).xlsx
@@ -402,7 +402,7 @@
         <v/>
       </c>
       <c r="C1" t="str">
-        <v>07/02/23 23:29:58</v>
+        <v>08/02/23 20:06:04</v>
       </c>
     </row>
     <row r="4">
@@ -426,34 +426,34 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>1028.66</v>
+        <v>1025.14</v>
       </c>
       <c r="B7" t="str">
-        <v>-4.29 (-0.4153%)</v>
+        <v>-3.52 (-0.3421%)</v>
       </c>
       <c r="C7" t="str">
         <v>High</v>
       </c>
       <c r="D7">
-        <v>1035.46</v>
+        <v>1032.1</v>
       </c>
       <c r="E7" t="str">
         <v>Low</v>
       </c>
       <c r="F7">
-        <v>1022.95</v>
+        <v>1021.69</v>
       </c>
       <c r="G7" t="str">
         <v>Volume</v>
       </c>
       <c r="H7">
-        <v>400196943</v>
+        <v>303511077</v>
       </c>
       <c r="I7" t="str">
         <v>Value</v>
       </c>
       <c r="J7">
-        <v>8689032478.01</v>
+        <v>7099762275.04</v>
       </c>
     </row>
     <row r="9">
@@ -514,19 +514,19 @@
         <v>-</v>
       </c>
       <c r="C10">
+        <v>21</v>
+      </c>
+      <c r="D10">
+        <v>-0.1</v>
+      </c>
+      <c r="E10">
+        <v>-0.47393364928909953</v>
+      </c>
+      <c r="F10">
         <v>21.1</v>
       </c>
-      <c r="D10">
-        <v>-0.2</v>
-      </c>
-      <c r="E10">
-        <v>-0.9389671361502347</v>
-      </c>
-      <c r="F10">
-        <v>21.3</v>
-      </c>
       <c r="G10">
-        <v>21.4</v>
+        <v>21.1</v>
       </c>
       <c r="H10">
         <v>20.9</v>
@@ -538,13 +538,13 @@
         <v>0</v>
       </c>
       <c r="K10">
-        <v>11021734</v>
+        <v>3154617</v>
       </c>
       <c r="L10">
-        <v>232419.2244</v>
+        <v>66212.80129999999</v>
       </c>
       <c r="M10">
-        <v>2048300</v>
+        <v>962800</v>
       </c>
       <c r="N10">
         <v>21</v>
@@ -553,7 +553,7 @@
         <v>21.1</v>
       </c>
       <c r="P10">
-        <v>189800</v>
+        <v>261500</v>
       </c>
     </row>
     <row r="11">
@@ -567,43 +567,43 @@
         <v>29.5</v>
       </c>
       <c r="D11">
-        <v>-0.25</v>
+        <v>0</v>
       </c>
       <c r="E11">
-        <v>-0.8403361344537815</v>
+        <v>0</v>
       </c>
       <c r="F11">
-        <v>30</v>
+        <v>29.75</v>
       </c>
       <c r="G11">
         <v>30</v>
       </c>
       <c r="H11">
+        <v>29.25</v>
+      </c>
+      <c r="I11">
+        <v>570000</v>
+      </c>
+      <c r="J11">
+        <v>16815</v>
+      </c>
+      <c r="K11">
+        <v>27537710</v>
+      </c>
+      <c r="L11">
+        <v>814225.86</v>
+      </c>
+      <c r="M11">
+        <v>7226400</v>
+      </c>
+      <c r="N11">
+        <v>29.25</v>
+      </c>
+      <c r="O11">
         <v>29.5</v>
       </c>
-      <c r="I11">
-        <v>0</v>
-      </c>
-      <c r="J11">
-        <v>0</v>
-      </c>
-      <c r="K11">
-        <v>21781654</v>
-      </c>
-      <c r="L11">
-        <v>646621.64125</v>
-      </c>
-      <c r="M11">
-        <v>9700400</v>
-      </c>
-      <c r="N11">
-        <v>29.5</v>
-      </c>
-      <c r="O11">
-        <v>29.75</v>
-      </c>
       <c r="P11">
-        <v>1863000</v>
+        <v>2960000</v>
       </c>
     </row>
     <row r="12">
@@ -614,19 +614,19 @@
         <v>-</v>
       </c>
       <c r="C12">
+        <v>9.65</v>
+      </c>
+      <c r="D12">
+        <v>0.05</v>
+      </c>
+      <c r="E12">
+        <v>0.5208333333333334</v>
+      </c>
+      <c r="F12">
         <v>9.6</v>
       </c>
-      <c r="D12">
-        <v>-0.15</v>
-      </c>
-      <c r="E12">
-        <v>-1.5384615384615385</v>
-      </c>
-      <c r="F12">
-        <v>9.7</v>
-      </c>
       <c r="G12">
-        <v>9.75</v>
+        <v>9.65</v>
       </c>
       <c r="H12">
         <v>9.55</v>
@@ -638,13 +638,13 @@
         <v>0</v>
       </c>
       <c r="K12">
-        <v>58793587</v>
+        <v>37282411</v>
       </c>
       <c r="L12">
-        <v>565334.3098500001</v>
+        <v>358143.69605</v>
       </c>
       <c r="M12">
-        <v>1211000</v>
+        <v>5826400</v>
       </c>
       <c r="N12">
         <v>9.6</v>
@@ -653,7 +653,7 @@
         <v>9.65</v>
       </c>
       <c r="P12">
-        <v>3215400</v>
+        <v>1946600</v>
       </c>
     </row>
     <row r="13">
@@ -667,43 +667,43 @@
         <v>214</v>
       </c>
       <c r="D13">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="E13">
-        <v>-0.46511627906976744</v>
+        <v>0</v>
       </c>
       <c r="F13">
+        <v>215</v>
+      </c>
+      <c r="G13">
+        <v>216</v>
+      </c>
+      <c r="H13">
+        <v>212</v>
+      </c>
+      <c r="I13">
+        <v>4600</v>
+      </c>
+      <c r="J13">
+        <v>984.4</v>
+      </c>
+      <c r="K13">
+        <v>2703727</v>
+      </c>
+      <c r="L13">
+        <v>577269.675</v>
+      </c>
+      <c r="M13">
+        <v>68600</v>
+      </c>
+      <c r="N13">
+        <v>213</v>
+      </c>
+      <c r="O13">
         <v>214</v>
       </c>
-      <c r="G13">
-        <v>215</v>
-      </c>
-      <c r="H13">
-        <v>211</v>
-      </c>
-      <c r="I13">
-        <v>13600</v>
-      </c>
-      <c r="J13">
-        <v>2910.4</v>
-      </c>
-      <c r="K13">
-        <v>2593682</v>
-      </c>
-      <c r="L13">
-        <v>553752.373</v>
-      </c>
-      <c r="M13">
-        <v>315500</v>
-      </c>
-      <c r="N13">
-        <v>214</v>
-      </c>
-      <c r="O13">
-        <v>215</v>
-      </c>
       <c r="P13">
-        <v>204300</v>
+        <v>202800</v>
       </c>
     </row>
     <row r="14">
@@ -714,22 +714,22 @@
         <v>-</v>
       </c>
       <c r="C14">
+        <v>38.75</v>
+      </c>
+      <c r="D14">
+        <v>0.25</v>
+      </c>
+      <c r="E14">
+        <v>0.6493506493506493</v>
+      </c>
+      <c r="F14">
         <v>38.5</v>
       </c>
-      <c r="D14">
-        <v>0.5</v>
-      </c>
-      <c r="E14">
-        <v>1.3157894736842106</v>
-      </c>
-      <c r="F14">
-        <v>38.25</v>
-      </c>
       <c r="G14">
-        <v>38.75</v>
+        <v>39.5</v>
       </c>
       <c r="H14">
-        <v>37.5</v>
+        <v>38.5</v>
       </c>
       <c r="I14">
         <v>0</v>
@@ -738,13 +738,13 @@
         <v>0</v>
       </c>
       <c r="K14">
-        <v>4774943</v>
+        <v>10373715</v>
       </c>
       <c r="L14">
-        <v>182526.64975</v>
+        <v>403408.98225</v>
       </c>
       <c r="M14">
-        <v>374200</v>
+        <v>18100</v>
       </c>
       <c r="N14">
         <v>38.5</v>
@@ -753,7 +753,7 @@
         <v>38.75</v>
       </c>
       <c r="P14">
-        <v>403100</v>
+        <v>102600</v>
       </c>
     </row>
     <row r="15">
@@ -764,19 +764,19 @@
         <v>-</v>
       </c>
       <c r="C15">
-        <v>8.25</v>
+        <v>8.2</v>
       </c>
       <c r="D15">
         <v>-0.05</v>
       </c>
       <c r="E15">
-        <v>-0.6024096385542169</v>
+        <v>-0.6060606060606061</v>
       </c>
       <c r="F15">
         <v>8.3</v>
       </c>
       <c r="G15">
-        <v>8.4</v>
+        <v>8.3</v>
       </c>
       <c r="H15">
         <v>8.2</v>
@@ -788,22 +788,22 @@
         <v>0</v>
       </c>
       <c r="K15">
-        <v>52782066</v>
+        <v>23116540</v>
       </c>
       <c r="L15">
-        <v>436595.46095</v>
+        <v>190510.177</v>
       </c>
       <c r="M15">
-        <v>267700</v>
+        <v>6632600</v>
       </c>
       <c r="N15">
+        <v>8.2</v>
+      </c>
+      <c r="O15">
         <v>8.25</v>
       </c>
-      <c r="O15">
-        <v>8.3</v>
-      </c>
       <c r="P15">
-        <v>1769900</v>
+        <v>1478800</v>
       </c>
     </row>
     <row r="16">
@@ -814,46 +814,46 @@
         <v>-</v>
       </c>
       <c r="C16">
-        <v>102</v>
+        <v>100.5</v>
       </c>
       <c r="D16">
-        <v>-1</v>
+        <v>-1.5</v>
       </c>
       <c r="E16">
-        <v>-0.970873786407767</v>
+        <v>-1.4705882352941178</v>
       </c>
       <c r="F16">
-        <v>103</v>
+        <v>102.5</v>
       </c>
       <c r="G16">
-        <v>103.5</v>
+        <v>102.5</v>
       </c>
       <c r="H16">
-        <v>101.5</v>
+        <v>100.5</v>
       </c>
       <c r="I16">
-        <v>0</v>
+        <v>88000</v>
       </c>
       <c r="J16">
-        <v>0</v>
+        <v>8844</v>
       </c>
       <c r="K16">
-        <v>1768116</v>
+        <v>1844304</v>
       </c>
       <c r="L16">
-        <v>180572.946</v>
+        <v>186542.3475</v>
       </c>
       <c r="M16">
-        <v>151600</v>
+        <v>269000</v>
       </c>
       <c r="N16">
-        <v>101.5</v>
+        <v>100.5</v>
       </c>
       <c r="O16">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="P16">
-        <v>63900</v>
+        <v>24500</v>
       </c>
     </row>
     <row r="17">
@@ -864,46 +864,46 @@
         <v>-</v>
       </c>
       <c r="C17">
+        <v>3.86</v>
+      </c>
+      <c r="D17">
+        <v>-0.02</v>
+      </c>
+      <c r="E17">
+        <v>-0.5154639175257731</v>
+      </c>
+      <c r="F17">
         <v>3.88</v>
       </c>
-      <c r="D17">
-        <v>-0.04</v>
-      </c>
-      <c r="E17">
-        <v>-1.0204081632653061</v>
-      </c>
-      <c r="F17">
-        <v>3.92</v>
-      </c>
       <c r="G17">
-        <v>3.92</v>
+        <v>3.88</v>
       </c>
       <c r="H17">
+        <v>3.82</v>
+      </c>
+      <c r="I17">
+        <v>0</v>
+      </c>
+      <c r="J17">
+        <v>0</v>
+      </c>
+      <c r="K17">
+        <v>15465710</v>
+      </c>
+      <c r="L17">
+        <v>59680.096979999995</v>
+      </c>
+      <c r="M17">
+        <v>962000</v>
+      </c>
+      <c r="N17">
         <v>3.84</v>
       </c>
-      <c r="I17">
-        <v>0</v>
-      </c>
-      <c r="J17">
-        <v>0</v>
-      </c>
-      <c r="K17">
-        <v>34601807</v>
-      </c>
-      <c r="L17">
-        <v>133738.43502</v>
-      </c>
-      <c r="M17">
-        <v>1579900</v>
-      </c>
-      <c r="N17">
+      <c r="O17">
         <v>3.86</v>
       </c>
-      <c r="O17">
-        <v>3.88</v>
-      </c>
       <c r="P17">
-        <v>1263300</v>
+        <v>654700</v>
       </c>
     </row>
     <row r="18">
@@ -914,13 +914,13 @@
         <v>-</v>
       </c>
       <c r="C18">
-        <v>31.75</v>
+        <v>31.5</v>
       </c>
       <c r="D18">
-        <v>-0.5</v>
+        <v>-0.25</v>
       </c>
       <c r="E18">
-        <v>-1.550387596899225</v>
+        <v>-0.7874015748031497</v>
       </c>
       <c r="F18">
         <v>32</v>
@@ -932,28 +932,28 @@
         <v>31.25</v>
       </c>
       <c r="I18">
-        <v>7133000</v>
+        <v>555400</v>
       </c>
       <c r="J18">
-        <v>228106</v>
+        <v>17495.1</v>
       </c>
       <c r="K18">
-        <v>15549744</v>
+        <v>7042142</v>
       </c>
       <c r="L18">
-        <v>495102.87975</v>
+        <v>222528.6925</v>
       </c>
       <c r="M18">
-        <v>265700</v>
+        <v>1178100</v>
       </c>
       <c r="N18">
-        <v>31.75</v>
+        <v>31.25</v>
       </c>
       <c r="O18">
-        <v>32</v>
+        <v>31.5</v>
       </c>
       <c r="P18">
-        <v>667600</v>
+        <v>141700</v>
       </c>
     </row>
     <row r="19">
@@ -973,37 +973,37 @@
         <v>0</v>
       </c>
       <c r="F19">
-        <v>66.5</v>
+        <v>66.75</v>
       </c>
       <c r="G19">
-        <v>67</v>
+        <v>67.25</v>
       </c>
       <c r="H19">
         <v>66.5</v>
       </c>
       <c r="I19">
-        <v>0</v>
+        <v>46000</v>
       </c>
       <c r="J19">
-        <v>0</v>
+        <v>3070.5</v>
       </c>
       <c r="K19">
-        <v>17353807</v>
+        <v>8511118</v>
       </c>
       <c r="L19">
-        <v>1158120.88375</v>
+        <v>569282.9895</v>
       </c>
       <c r="M19">
-        <v>2792200</v>
+        <v>1263500</v>
       </c>
       <c r="N19">
+        <v>66.5</v>
+      </c>
+      <c r="O19">
         <v>66.75</v>
       </c>
-      <c r="O19">
-        <v>67</v>
-      </c>
       <c r="P19">
-        <v>1848100</v>
+        <v>628500</v>
       </c>
     </row>
     <row r="20">
@@ -1014,46 +1014,46 @@
         <v>-</v>
       </c>
       <c r="C20">
-        <v>23.6</v>
+        <v>23.3</v>
       </c>
       <c r="D20">
-        <v>0</v>
+        <v>-0.3</v>
       </c>
       <c r="E20">
-        <v>0</v>
+        <v>-1.271186440677966</v>
       </c>
       <c r="F20">
         <v>23.6</v>
       </c>
       <c r="G20">
-        <v>23.7</v>
+        <v>23.6</v>
       </c>
       <c r="H20">
-        <v>23.5</v>
+        <v>23.3</v>
       </c>
       <c r="I20">
-        <v>0</v>
+        <v>3472000</v>
       </c>
       <c r="J20">
-        <v>0</v>
+        <v>80897.6</v>
       </c>
       <c r="K20">
-        <v>17028962</v>
+        <v>28889712</v>
       </c>
       <c r="L20">
-        <v>401183.07739999995</v>
+        <v>675575.3047999999</v>
       </c>
       <c r="M20">
-        <v>2056100</v>
+        <v>5431700</v>
       </c>
       <c r="N20">
-        <v>23.5</v>
+        <v>23.3</v>
       </c>
       <c r="O20">
-        <v>23.6</v>
+        <v>23.4</v>
       </c>
       <c r="P20">
-        <v>347500</v>
+        <v>1514900</v>
       </c>
     </row>
     <row r="21">
@@ -1067,19 +1067,19 @@
         <v>44.25</v>
       </c>
       <c r="D21">
-        <v>-0.25</v>
+        <v>0</v>
       </c>
       <c r="E21">
-        <v>-0.5617977528089888</v>
+        <v>0</v>
       </c>
       <c r="F21">
-        <v>44.5</v>
+        <v>44.25</v>
       </c>
       <c r="G21">
         <v>44.5</v>
       </c>
       <c r="H21">
-        <v>43.75</v>
+        <v>44</v>
       </c>
       <c r="I21">
         <v>0</v>
@@ -1088,13 +1088,13 @@
         <v>0</v>
       </c>
       <c r="K21">
-        <v>10167453</v>
+        <v>11168771</v>
       </c>
       <c r="L21">
-        <v>448185.82275</v>
+        <v>493385.741</v>
       </c>
       <c r="M21">
-        <v>667100</v>
+        <v>947000</v>
       </c>
       <c r="N21">
         <v>44</v>
@@ -1103,7 +1103,7 @@
         <v>44.25</v>
       </c>
       <c r="P21">
-        <v>1198400</v>
+        <v>1021800</v>
       </c>
     </row>
     <row r="22">
@@ -1114,22 +1114,22 @@
         <v>-</v>
       </c>
       <c r="C22">
+        <v>13.7</v>
+      </c>
+      <c r="D22">
+        <v>-0.2</v>
+      </c>
+      <c r="E22">
+        <v>-1.4388489208633093</v>
+      </c>
+      <c r="F22">
         <v>13.9</v>
       </c>
-      <c r="D22">
-        <v>-0.1</v>
-      </c>
-      <c r="E22">
-        <v>-0.7142857142857143</v>
-      </c>
-      <c r="F22">
+      <c r="G22">
         <v>14</v>
       </c>
-      <c r="G22">
-        <v>14.1</v>
-      </c>
       <c r="H22">
-        <v>13.8</v>
+        <v>13.6</v>
       </c>
       <c r="I22">
         <v>0</v>
@@ -1138,22 +1138,22 @@
         <v>0</v>
       </c>
       <c r="K22">
-        <v>8237603</v>
+        <v>9695078</v>
       </c>
       <c r="L22">
-        <v>114980.3154</v>
+        <v>133452.0775</v>
       </c>
       <c r="M22">
-        <v>348700</v>
+        <v>1337800</v>
       </c>
       <c r="N22">
-        <v>13.9</v>
+        <v>13.6</v>
       </c>
       <c r="O22">
-        <v>14</v>
+        <v>13.7</v>
       </c>
       <c r="P22">
-        <v>1020100</v>
+        <v>106300</v>
       </c>
     </row>
     <row r="23">
@@ -1164,13 +1164,13 @@
         <v>-</v>
       </c>
       <c r="C23">
-        <v>20.9</v>
+        <v>20.8</v>
       </c>
       <c r="D23">
-        <v>0</v>
+        <v>-0.1</v>
       </c>
       <c r="E23">
-        <v>0</v>
+        <v>-0.4784688995215311</v>
       </c>
       <c r="F23">
         <v>20.9</v>
@@ -1182,28 +1182,28 @@
         <v>20.7</v>
       </c>
       <c r="I23">
-        <v>0</v>
+        <v>200000</v>
       </c>
       <c r="J23">
-        <v>0</v>
+        <v>4180</v>
       </c>
       <c r="K23">
-        <v>11074770</v>
+        <v>8045090</v>
       </c>
       <c r="L23">
-        <v>230826.29940000002</v>
+        <v>167697.2623</v>
       </c>
       <c r="M23">
-        <v>9800</v>
+        <v>797800</v>
       </c>
       <c r="N23">
-        <v>20.9</v>
+        <v>20.7</v>
       </c>
       <c r="O23">
-        <v>21</v>
+        <v>20.8</v>
       </c>
       <c r="P23">
-        <v>851900</v>
+        <v>3900</v>
       </c>
     </row>
     <row r="24">
@@ -1214,13 +1214,13 @@
         <v>-</v>
       </c>
       <c r="C24">
-        <v>14.7</v>
+        <v>14.6</v>
       </c>
       <c r="D24">
-        <v>0</v>
+        <v>-0.1</v>
       </c>
       <c r="E24">
-        <v>0</v>
+        <v>-0.6802721088435374</v>
       </c>
       <c r="F24">
         <v>14.7</v>
@@ -1229,31 +1229,31 @@
         <v>14.8</v>
       </c>
       <c r="H24">
+        <v>14.4</v>
+      </c>
+      <c r="I24">
+        <v>1076500</v>
+      </c>
+      <c r="J24">
+        <v>15770.725</v>
+      </c>
+      <c r="K24">
+        <v>33282084</v>
+      </c>
+      <c r="L24">
+        <v>485581.9636</v>
+      </c>
+      <c r="M24">
+        <v>1698500</v>
+      </c>
+      <c r="N24">
+        <v>14.5</v>
+      </c>
+      <c r="O24">
         <v>14.6</v>
       </c>
-      <c r="I24">
-        <v>0</v>
-      </c>
-      <c r="J24">
-        <v>0</v>
-      </c>
-      <c r="K24">
-        <v>11804881</v>
-      </c>
-      <c r="L24">
-        <v>173815.2965</v>
-      </c>
-      <c r="M24">
-        <v>2315500</v>
-      </c>
-      <c r="N24">
-        <v>14.7</v>
-      </c>
-      <c r="O24">
-        <v>14.8</v>
-      </c>
       <c r="P24">
-        <v>1376800</v>
+        <v>1132700</v>
       </c>
     </row>
     <row r="25">
@@ -1264,46 +1264,46 @@
         <v>-</v>
       </c>
       <c r="C25">
+        <v>20.4</v>
+      </c>
+      <c r="D25">
+        <v>-0.3</v>
+      </c>
+      <c r="E25">
+        <v>-1.4492753623188406</v>
+      </c>
+      <c r="F25">
         <v>20.7</v>
       </c>
-      <c r="D25">
-        <v>-0.2</v>
-      </c>
-      <c r="E25">
-        <v>-0.9569377990430622</v>
-      </c>
-      <c r="F25">
-        <v>20.8</v>
-      </c>
       <c r="G25">
-        <v>21</v>
+        <v>20.7</v>
       </c>
       <c r="H25">
+        <v>19.9</v>
+      </c>
+      <c r="I25">
+        <v>0</v>
+      </c>
+      <c r="J25">
+        <v>0</v>
+      </c>
+      <c r="K25">
+        <v>7581343</v>
+      </c>
+      <c r="L25">
+        <v>153631.8931</v>
+      </c>
+      <c r="M25">
+        <v>479600</v>
+      </c>
+      <c r="N25">
+        <v>20.4</v>
+      </c>
+      <c r="O25">
         <v>20.5</v>
       </c>
-      <c r="I25">
-        <v>0</v>
-      </c>
-      <c r="J25">
-        <v>0</v>
-      </c>
-      <c r="K25">
-        <v>5033514</v>
-      </c>
-      <c r="L25">
-        <v>104421.0835</v>
-      </c>
-      <c r="M25">
-        <v>167300</v>
-      </c>
-      <c r="N25">
-        <v>20.6</v>
-      </c>
-      <c r="O25">
-        <v>20.7</v>
-      </c>
       <c r="P25">
-        <v>10300</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="26">
@@ -1314,46 +1314,46 @@
         <v>-</v>
       </c>
       <c r="C26">
-        <v>18.3</v>
+        <v>18.1</v>
       </c>
       <c r="D26">
-        <v>-0.3</v>
+        <v>-0.2</v>
       </c>
       <c r="E26">
-        <v>-1.6129032258064515</v>
+        <v>-1.092896174863388</v>
       </c>
       <c r="F26">
-        <v>18.6</v>
+        <v>18.4</v>
       </c>
       <c r="G26">
-        <v>18.7</v>
+        <v>18.4</v>
       </c>
       <c r="H26">
+        <v>18.1</v>
+      </c>
+      <c r="I26">
+        <v>0</v>
+      </c>
+      <c r="J26">
+        <v>0</v>
+      </c>
+      <c r="K26">
+        <v>2402994</v>
+      </c>
+      <c r="L26">
+        <v>43820.721</v>
+      </c>
+      <c r="M26">
+        <v>163700</v>
+      </c>
+      <c r="N26">
+        <v>18.1</v>
+      </c>
+      <c r="O26">
         <v>18.2</v>
       </c>
-      <c r="I26">
-        <v>0</v>
-      </c>
-      <c r="J26">
-        <v>0</v>
-      </c>
-      <c r="K26">
-        <v>2231293</v>
-      </c>
-      <c r="L26">
-        <v>40973.5248</v>
-      </c>
-      <c r="M26">
-        <v>130400</v>
-      </c>
-      <c r="N26">
-        <v>18.3</v>
-      </c>
-      <c r="O26">
-        <v>18.4</v>
-      </c>
       <c r="P26">
-        <v>30900</v>
+        <v>18400</v>
       </c>
     </row>
     <row r="27">
@@ -1364,46 +1364,46 @@
         <v>-</v>
       </c>
       <c r="C27">
-        <v>56.25</v>
+        <v>55.75</v>
       </c>
       <c r="D27">
         <v>-0.5</v>
       </c>
       <c r="E27">
-        <v>-0.8810572687224669</v>
+        <v>-0.8888888888888888</v>
       </c>
       <c r="F27">
-        <v>56.75</v>
+        <v>56</v>
       </c>
       <c r="G27">
-        <v>57</v>
+        <v>56.5</v>
       </c>
       <c r="H27">
+        <v>55.5</v>
+      </c>
+      <c r="I27">
+        <v>0</v>
+      </c>
+      <c r="J27">
+        <v>0</v>
+      </c>
+      <c r="K27">
+        <v>787982</v>
+      </c>
+      <c r="L27">
+        <v>44082.099</v>
+      </c>
+      <c r="M27">
+        <v>35600</v>
+      </c>
+      <c r="N27">
+        <v>55.75</v>
+      </c>
+      <c r="O27">
         <v>56</v>
       </c>
-      <c r="I27">
-        <v>0</v>
-      </c>
-      <c r="J27">
-        <v>0</v>
-      </c>
-      <c r="K27">
-        <v>1610798</v>
-      </c>
-      <c r="L27">
-        <v>90754.65875</v>
-      </c>
-      <c r="M27">
-        <v>165800</v>
-      </c>
-      <c r="N27">
-        <v>56.25</v>
-      </c>
-      <c r="O27">
-        <v>56.5</v>
-      </c>
       <c r="P27">
-        <v>77200</v>
+        <v>7800</v>
       </c>
     </row>
     <row r="28">
@@ -1414,22 +1414,22 @@
         <v>-</v>
       </c>
       <c r="C28">
+        <v>50.75</v>
+      </c>
+      <c r="D28">
+        <v>-0.75</v>
+      </c>
+      <c r="E28">
+        <v>-1.4563106796116505</v>
+      </c>
+      <c r="F28">
         <v>51.5</v>
-      </c>
-      <c r="D28">
-        <v>-0.25</v>
-      </c>
-      <c r="E28">
-        <v>-0.4830917874396135</v>
-      </c>
-      <c r="F28">
-        <v>51.75</v>
       </c>
       <c r="G28">
         <v>52</v>
       </c>
       <c r="H28">
-        <v>50.5</v>
+        <v>50.75</v>
       </c>
       <c r="I28">
         <v>0</v>
@@ -1438,22 +1438,22 @@
         <v>0</v>
       </c>
       <c r="K28">
-        <v>2419856</v>
+        <v>1412541</v>
       </c>
       <c r="L28">
-        <v>124190.05275</v>
+        <v>72185.227</v>
       </c>
       <c r="M28">
-        <v>307500</v>
+        <v>103800</v>
       </c>
       <c r="N28">
-        <v>51.5</v>
+        <v>50.75</v>
       </c>
       <c r="O28">
-        <v>51.75</v>
+        <v>51</v>
       </c>
       <c r="P28">
-        <v>22200</v>
+        <v>16500</v>
       </c>
     </row>
     <row r="29">
@@ -1464,37 +1464,37 @@
         <v>-</v>
       </c>
       <c r="C29">
+        <v>28.25</v>
+      </c>
+      <c r="D29">
+        <v>-0.25</v>
+      </c>
+      <c r="E29">
+        <v>-0.8771929824561403</v>
+      </c>
+      <c r="F29">
         <v>28.5</v>
-      </c>
-      <c r="D29">
-        <v>0.25</v>
-      </c>
-      <c r="E29">
-        <v>0.8849557522123894</v>
-      </c>
-      <c r="F29">
-        <v>28.25</v>
       </c>
       <c r="G29">
         <v>28.5</v>
       </c>
       <c r="H29">
-        <v>28</v>
+        <v>28.25</v>
       </c>
       <c r="I29">
-        <v>0</v>
+        <v>804100</v>
       </c>
       <c r="J29">
-        <v>0</v>
+        <v>22715.825</v>
       </c>
       <c r="K29">
-        <v>5471542</v>
+        <v>2828867</v>
       </c>
       <c r="L29">
-        <v>154774.204</v>
+        <v>79952.18825</v>
       </c>
       <c r="M29">
-        <v>760700</v>
+        <v>1505600</v>
       </c>
       <c r="N29">
         <v>28.25</v>
@@ -1503,7 +1503,7 @@
         <v>28.5</v>
       </c>
       <c r="P29">
-        <v>714100</v>
+        <v>753900</v>
       </c>
     </row>
     <row r="30">
@@ -1514,19 +1514,19 @@
         <v>-</v>
       </c>
       <c r="C30">
-        <v>54.25</v>
+        <v>54</v>
       </c>
       <c r="D30">
         <v>-0.25</v>
       </c>
       <c r="E30">
-        <v>-0.45871559633027525</v>
+        <v>-0.4608294930875576</v>
       </c>
       <c r="F30">
-        <v>54.75</v>
+        <v>54.25</v>
       </c>
       <c r="G30">
-        <v>54.75</v>
+        <v>54.25</v>
       </c>
       <c r="H30">
         <v>54</v>
@@ -1538,13 +1538,13 @@
         <v>0</v>
       </c>
       <c r="K30">
-        <v>119773</v>
+        <v>201909</v>
       </c>
       <c r="L30">
-        <v>6501.21925</v>
+        <v>10911.59975</v>
       </c>
       <c r="M30">
-        <v>112400</v>
+        <v>96600</v>
       </c>
       <c r="N30">
         <v>54</v>
@@ -1553,7 +1553,7 @@
         <v>54.25</v>
       </c>
       <c r="P30">
-        <v>4600</v>
+        <v>28900</v>
       </c>
     </row>
     <row r="31">
@@ -1564,22 +1564,22 @@
         <v>-</v>
       </c>
       <c r="C31">
+        <v>12.6</v>
+      </c>
+      <c r="D31">
+        <v>-0.3</v>
+      </c>
+      <c r="E31">
+        <v>-2.3255813953488373</v>
+      </c>
+      <c r="F31">
         <v>12.9</v>
       </c>
-      <c r="D31">
-        <v>0.1</v>
-      </c>
-      <c r="E31">
-        <v>0.78125</v>
-      </c>
-      <c r="F31">
-        <v>12.8</v>
-      </c>
       <c r="G31">
-        <v>13</v>
+        <v>12.9</v>
       </c>
       <c r="H31">
-        <v>12.8</v>
+        <v>12.6</v>
       </c>
       <c r="I31">
         <v>0</v>
@@ -1588,22 +1588,22 @@
         <v>0</v>
       </c>
       <c r="K31">
-        <v>3377331</v>
+        <v>2864614</v>
       </c>
       <c r="L31">
-        <v>43600.9581</v>
+        <v>36429.1913</v>
       </c>
       <c r="M31">
-        <v>334900</v>
+        <v>164700</v>
       </c>
       <c r="N31">
-        <v>12.8</v>
+        <v>12.6</v>
       </c>
       <c r="O31">
-        <v>12.9</v>
+        <v>12.7</v>
       </c>
       <c r="P31">
-        <v>419300</v>
+        <v>204100</v>
       </c>
     </row>
     <row r="32">
@@ -1614,13 +1614,13 @@
         <v>-</v>
       </c>
       <c r="C32">
-        <v>31</v>
+        <v>30.5</v>
       </c>
       <c r="D32">
-        <v>0</v>
+        <v>-0.5</v>
       </c>
       <c r="E32">
-        <v>0</v>
+        <v>-1.6129032258064515</v>
       </c>
       <c r="F32">
         <v>31</v>
@@ -1629,31 +1629,31 @@
         <v>31.25</v>
       </c>
       <c r="H32">
+        <v>30.5</v>
+      </c>
+      <c r="I32">
+        <v>0</v>
+      </c>
+      <c r="J32">
+        <v>0</v>
+      </c>
+      <c r="K32">
+        <v>2338011</v>
+      </c>
+      <c r="L32">
+        <v>71924.69825</v>
+      </c>
+      <c r="M32">
+        <v>547600</v>
+      </c>
+      <c r="N32">
+        <v>30.5</v>
+      </c>
+      <c r="O32">
         <v>30.75</v>
       </c>
-      <c r="I32">
-        <v>0</v>
-      </c>
-      <c r="J32">
-        <v>0</v>
-      </c>
-      <c r="K32">
-        <v>1864108</v>
-      </c>
-      <c r="L32">
-        <v>57752.77575</v>
-      </c>
-      <c r="M32">
-        <v>385200</v>
-      </c>
-      <c r="N32">
-        <v>30.75</v>
-      </c>
-      <c r="O32">
-        <v>31</v>
-      </c>
       <c r="P32">
-        <v>96800</v>
+        <v>42900</v>
       </c>
     </row>
     <row r="33">
@@ -1664,46 +1664,46 @@
         <v>-</v>
       </c>
       <c r="C33">
+        <v>12.9</v>
+      </c>
+      <c r="D33">
+        <v>-0.1</v>
+      </c>
+      <c r="E33">
+        <v>-0.7692307692307693</v>
+      </c>
+      <c r="F33">
+        <v>13.1</v>
+      </c>
+      <c r="G33">
+        <v>13.2</v>
+      </c>
+      <c r="H33">
+        <v>12.8</v>
+      </c>
+      <c r="I33">
+        <v>0</v>
+      </c>
+      <c r="J33">
+        <v>0</v>
+      </c>
+      <c r="K33">
+        <v>13513684</v>
+      </c>
+      <c r="L33">
+        <v>175403.0711</v>
+      </c>
+      <c r="M33">
+        <v>393800</v>
+      </c>
+      <c r="N33">
+        <v>12.9</v>
+      </c>
+      <c r="O33">
         <v>13</v>
       </c>
-      <c r="D33">
-        <v>-0.4</v>
-      </c>
-      <c r="E33">
-        <v>-2.985074626865672</v>
-      </c>
-      <c r="F33">
-        <v>13.5</v>
-      </c>
-      <c r="G33">
-        <v>13.5</v>
-      </c>
-      <c r="H33">
-        <v>13</v>
-      </c>
-      <c r="I33">
-        <v>0</v>
-      </c>
-      <c r="J33">
-        <v>0</v>
-      </c>
-      <c r="K33">
-        <v>41170399</v>
-      </c>
-      <c r="L33">
-        <v>542325.5884</v>
-      </c>
-      <c r="M33">
-        <v>104800</v>
-      </c>
-      <c r="N33">
-        <v>13</v>
-      </c>
-      <c r="O33">
-        <v>13.1</v>
-      </c>
       <c r="P33">
-        <v>359200</v>
+        <v>488900</v>
       </c>
     </row>
     <row r="34">
@@ -1714,22 +1714,22 @@
         <v>-</v>
       </c>
       <c r="C34">
+        <v>27</v>
+      </c>
+      <c r="D34">
+        <v>-1</v>
+      </c>
+      <c r="E34">
+        <v>-3.5714285714285716</v>
+      </c>
+      <c r="F34">
         <v>28</v>
       </c>
-      <c r="D34">
-        <v>-0.25</v>
-      </c>
-      <c r="E34">
-        <v>-0.8849557522123894</v>
-      </c>
-      <c r="F34">
-        <v>28.5</v>
-      </c>
       <c r="G34">
-        <v>28.5</v>
+        <v>28</v>
       </c>
       <c r="H34">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I34">
         <v>0</v>
@@ -1738,22 +1738,22 @@
         <v>0</v>
       </c>
       <c r="K34">
-        <v>1866964</v>
+        <v>4328606</v>
       </c>
       <c r="L34">
-        <v>52523.9265</v>
+        <v>118499.238</v>
       </c>
       <c r="M34">
-        <v>56300</v>
+        <v>525400</v>
       </c>
       <c r="N34">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="O34">
-        <v>28.25</v>
+        <v>27.25</v>
       </c>
       <c r="P34">
-        <v>79900</v>
+        <v>181200</v>
       </c>
     </row>
     <row r="35">
@@ -1764,22 +1764,22 @@
         <v>-</v>
       </c>
       <c r="C35">
+        <v>24.5</v>
+      </c>
+      <c r="D35">
+        <v>1.1</v>
+      </c>
+      <c r="E35">
+        <v>4.700854700854701</v>
+      </c>
+      <c r="F35">
         <v>23.4</v>
       </c>
-      <c r="D35">
-        <v>0.8</v>
-      </c>
-      <c r="E35">
-        <v>3.5398230088495577</v>
-      </c>
-      <c r="F35">
-        <v>22.6</v>
-      </c>
       <c r="G35">
-        <v>23.6</v>
+        <v>24.7</v>
       </c>
       <c r="H35">
-        <v>22.6</v>
+        <v>23.2</v>
       </c>
       <c r="I35">
         <v>0</v>
@@ -1788,22 +1788,22 @@
         <v>0</v>
       </c>
       <c r="K35">
-        <v>17792391</v>
+        <v>19405610</v>
       </c>
       <c r="L35">
-        <v>410653.2648</v>
+        <v>466050.1147</v>
       </c>
       <c r="M35">
-        <v>371800</v>
+        <v>614800</v>
       </c>
       <c r="N35">
-        <v>23.3</v>
+        <v>24.5</v>
       </c>
       <c r="O35">
-        <v>23.4</v>
+        <v>24.6</v>
       </c>
       <c r="P35">
-        <v>22700</v>
+        <v>237600</v>
       </c>
     </row>
     <row r="36">
@@ -1817,16 +1817,16 @@
         <v>68</v>
       </c>
       <c r="D36">
-        <v>-3.25</v>
+        <v>0</v>
       </c>
       <c r="E36">
-        <v>-4.56140350877193</v>
+        <v>0</v>
       </c>
       <c r="F36">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="G36">
-        <v>71.75</v>
+        <v>68.5</v>
       </c>
       <c r="H36">
         <v>67</v>
@@ -1838,22 +1838,22 @@
         <v>0</v>
       </c>
       <c r="K36">
-        <v>11758723</v>
+        <v>3398659</v>
       </c>
       <c r="L36">
-        <v>805737.68375</v>
+        <v>230156.0015</v>
       </c>
       <c r="M36">
-        <v>68100</v>
+        <v>136700</v>
       </c>
       <c r="N36">
+        <v>67.75</v>
+      </c>
+      <c r="O36">
         <v>68</v>
       </c>
-      <c r="O36">
-        <v>68.25</v>
-      </c>
       <c r="P36">
-        <v>55900</v>
+        <v>211800</v>
       </c>
     </row>
     <row r="37">
@@ -1864,19 +1864,19 @@
         <v>-</v>
       </c>
       <c r="C37">
-        <v>16.2</v>
+        <v>16.1</v>
       </c>
       <c r="D37">
-        <v>0</v>
+        <v>-0.1</v>
       </c>
       <c r="E37">
-        <v>0</v>
+        <v>-0.6172839506172839</v>
       </c>
       <c r="F37">
         <v>16.3</v>
       </c>
       <c r="G37">
-        <v>16.4</v>
+        <v>16.3</v>
       </c>
       <c r="H37">
         <v>16.1</v>
@@ -1888,22 +1888,22 @@
         <v>0</v>
       </c>
       <c r="K37">
-        <v>16289493</v>
+        <v>11030952</v>
       </c>
       <c r="L37">
-        <v>264277.7181</v>
+        <v>177788.1126</v>
       </c>
       <c r="M37">
-        <v>1328900</v>
+        <v>3467300</v>
       </c>
       <c r="N37">
+        <v>16.1</v>
+      </c>
+      <c r="O37">
         <v>16.2</v>
       </c>
-      <c r="O37">
-        <v>16.3</v>
-      </c>
       <c r="P37">
-        <v>1582700</v>
+        <v>1787400</v>
       </c>
     </row>
     <row r="38">
@@ -1914,19 +1914,19 @@
         <v>-</v>
       </c>
       <c r="C38">
+        <v>29</v>
+      </c>
+      <c r="D38">
+        <v>0.25</v>
+      </c>
+      <c r="E38">
+        <v>0.8695652173913043</v>
+      </c>
+      <c r="F38">
         <v>28.75</v>
       </c>
-      <c r="D38">
-        <v>-0.25</v>
-      </c>
-      <c r="E38">
-        <v>-0.8620689655172413</v>
-      </c>
-      <c r="F38">
+      <c r="G38">
         <v>29</v>
-      </c>
-      <c r="G38">
-        <v>29.25</v>
       </c>
       <c r="H38">
         <v>28.75</v>
@@ -1938,13 +1938,13 @@
         <v>0</v>
       </c>
       <c r="K38">
-        <v>298190</v>
+        <v>184860</v>
       </c>
       <c r="L38">
-        <v>8600.59175</v>
+        <v>5339.53575</v>
       </c>
       <c r="M38">
-        <v>1106000</v>
+        <v>868700</v>
       </c>
       <c r="N38">
         <v>28.75</v>
@@ -1953,7 +1953,7 @@
         <v>29</v>
       </c>
       <c r="P38">
-        <v>64100</v>
+        <v>256300</v>
       </c>
     </row>
     <row r="39">
@@ -1967,19 +1967,19 @@
         <v>2.78</v>
       </c>
       <c r="D39">
-        <v>0.04</v>
+        <v>0</v>
       </c>
       <c r="E39">
-        <v>1.4598540145985401</v>
+        <v>0</v>
       </c>
       <c r="F39">
-        <v>2.74</v>
+        <v>2.8</v>
       </c>
       <c r="G39">
         <v>2.8</v>
       </c>
       <c r="H39">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="I39">
         <v>0</v>
@@ -1988,13 +1988,13 @@
         <v>0</v>
       </c>
       <c r="K39">
-        <v>9523459</v>
+        <v>3062716</v>
       </c>
       <c r="L39">
-        <v>26306.11264</v>
+        <v>8468.41646</v>
       </c>
       <c r="M39">
-        <v>214400</v>
+        <v>11800</v>
       </c>
       <c r="N39">
         <v>2.76</v>
@@ -2003,7 +2003,7 @@
         <v>2.78</v>
       </c>
       <c r="P39">
-        <v>650900</v>
+        <v>665000</v>
       </c>
     </row>
   </sheetData>
